--- a/sports_forms/014_player_trading_form--sports_forms.xlsx
+++ b/sports_forms/014_player_trading_form--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1150,8 +1150,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'mlb'}</t>
+          <t>mlb</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'MLB'}</t>
+          <t>MLB</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'nfl'}</t>
+          <t>nfl</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'NFL'}</t>
+          <t>NFL</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'nba'}</t>
+          <t>nba</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'NBA'}</t>
+          <t>NBA</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'nhl'}</t>
+          <t>nhl</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'NHL'}</t>
+          <t>NHL</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'yankees'}</t>
+          <t>yankees</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Yankees'}</t>
+          <t>Yankees</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'dodgers'}</t>
+          <t>dodgers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Dodgers'}</t>
+          <t>Dodgers</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'lakers'}</t>
+          <t>lakers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Lakers'}</t>
+          <t>Lakers</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'celtics'}</t>
+          <t>celtics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Celtics'}</t>
+          <t>Celtics</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'quarterback'}</t>
+          <t>quarterback</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Quarterback'}</t>
+          <t>Quarterback</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'running_back'}</t>
+          <t>running_back</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Running Back'}</t>
+          <t>Running Back</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'wide_receiver'}</t>
+          <t>wide_receiver</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Wide Receiver'}</t>
+          <t>Wide Receiver</t>
         </is>
       </c>
     </row>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'1_year'}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': '1 year'}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'2_years'}</t>
+          <t>2_years</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': '2 years'}</t>
+          <t>2 years</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'3_years'}</t>
+          <t>3_years</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': '3 years'}</t>
+          <t>3 years</t>
         </is>
       </c>
     </row>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'4_years'}</t>
+          <t>4_years</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': '4 years'}</t>
+          <t>4 years</t>
         </is>
       </c>
     </row>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'trade'}</t>
+          <t>trade</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'trade'}</t>
+          <t>trade</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'draft'}</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'draft'}</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1502,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'yankees'}</t>
+          <t>yankees</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Yankees'}</t>
+          <t>Yankees</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'dodgers'}</t>
+          <t>dodgers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Dodgers'}</t>
+          <t>Dodgers</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'lakers'}</t>
+          <t>lakers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Lakers'}</t>
+          <t>Lakers</t>
         </is>
       </c>
     </row>
@@ -1553,12 +1553,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'celtics'}</t>
+          <t>celtics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Celtics'}</t>
+          <t>Celtics</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'yankees'}</t>
+          <t>yankees</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Yankees'}</t>
+          <t>Yankees</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'dodgers'}</t>
+          <t>dodgers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Dodgers'}</t>
+          <t>Dodgers</t>
         </is>
       </c>
     </row>
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'lakers'}</t>
+          <t>lakers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Lakers'}</t>
+          <t>Lakers</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'celtics'}</t>
+          <t>celtics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Celtics'}</t>
+          <t>Celtics</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'1_year'}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': '1 year'}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
@@ -1723,12 +1723,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'2_years'}</t>
+          <t>2_years</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': '2 years'}</t>
+          <t>2 years</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'3_years'}</t>
+          <t>3_years</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': '3 years'}</t>
+          <t>3 years</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'4_years'}</t>
+          <t>4_years</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': '4 years'}</t>
+          <t>4 years</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'1_year'}</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': '1 year'}</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'2_years'}</t>
+          <t>2_years</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': '2 years'}</t>
+          <t>2 years</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'3_years'}</t>
+          <t>3_years</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': '3 years'}</t>
+          <t>3 years</t>
         </is>
       </c>
     </row>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'4_years'}</t>
+          <t>4_years</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': '4 years'}</t>
+          <t>4 years</t>
         </is>
       </c>
     </row>
